--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2107-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2107-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C793B62-3748-4263-BE94-7B9E7ACA1A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC4A04C2-74CA-4D2B-8ECC-FC5C877C6F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{1A570D9E-1414-4337-A3B6-2878BDDC507C}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{D4B17857-F9EE-4B78-93A3-602F567A7E84}"/>
   </bookViews>
   <sheets>
     <sheet name="2107-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1490,29 +1490,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD963044-0AF1-44C4-8397-D419D0F7EA5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{148DB544-36E9-4D17-BEEE-6C492CDC6987}">
   <dimension ref="A1:X41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1546,7 +1545,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1582,7 +1581,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1634,7 +1633,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1702,7 +1701,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1774,7 +1773,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1846,7 +1845,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1918,7 +1917,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1990,7 +1989,7 @@
         <v>6.14</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2062,7 +2061,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2134,7 +2133,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2206,7 +2205,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2278,7 +2277,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2350,7 +2349,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2422,7 +2421,7 @@
         <v>6.18</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2494,7 +2493,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2566,7 +2565,7 @@
         <v>7.33</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2638,7 +2637,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2710,7 +2709,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2782,7 +2781,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2854,7 +2853,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2926,7 +2925,7 @@
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -2998,7 +2997,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3070,7 +3069,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3142,7 +3141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3214,7 +3213,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3286,7 +3285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3358,7 +3357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3430,7 +3429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2000</v>
       </c>
@@ -3502,7 +3501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>1999</v>
       </c>
@@ -3574,7 +3573,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>1998</v>
       </c>
@@ -3646,7 +3645,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1997</v>
       </c>
@@ -3718,7 +3717,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="34">
         <v>1996</v>
       </c>
@@ -3790,7 +3789,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1995</v>
       </c>
@@ -3862,7 +3861,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="34">
         <v>1994</v>
       </c>
@@ -3934,7 +3933,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1993</v>
       </c>
@@ -4006,7 +4005,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="34">
         <v>1992</v>
       </c>
@@ -4078,7 +4077,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1991</v>
       </c>
@@ -4150,7 +4149,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="34">
         <v>1990</v>
       </c>
@@ -4222,7 +4221,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>1988</v>
       </c>
@@ -4294,7 +4293,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="34" t="s">
         <v>55</v>
       </c>
